--- a/examples/tracker/basic/tracker_config.xlsx
+++ b/examples/tracker/basic/tracker_config.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="" yWindow="" windowWidth="" windowHeight="" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Waves" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,13 +12,32 @@
     <sheet name="Banner" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -29,15 +48,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -57,25 +76,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -432,20 +446,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,21 +624,22 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="40" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,20 +746,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -797,20 +813,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="30" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -921,7 +938,31 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>